--- a/BWI/bestwine_output/bestwine_Zambia.xlsx
+++ b/BWI/bestwine_output/bestwine_Zambia.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1623,6 +1623,107 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Liquify Enterprise Limited</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Liquify Enterprise Limited</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>99211</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Zambia</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Lusaka</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Lusaka Province</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1 Nelson Sapi Road, Chainama Road</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://liquify-zambia.com</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>support@liquify-zambia.com</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/liquify-enterprise-limited/</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>https://facebook.com/LiquifyZM</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/liquifyzm</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/LiquifyZM</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Evans Mauta II</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Executive Director</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/evans-mauta-ii/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Zambia.xlsx
+++ b/BWI/bestwine_output/bestwine_Zambia.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1724,6 +1724,495 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>BERKEMBER BOTTLE STORE</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>167902</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Zambia</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Lusaka</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Makeni Villa Plot Bp184-005, Los Angels Road Park</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://bottleshopzm.com</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>300587</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>posbottleshop@gmail.com</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>320190007770</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-bottleshop-zambia/</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bottleshopzm</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bottleshopzm/</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>Emmanuel Zulu</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Operations &amp; Inventory Manager</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emmanuelzux/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BERKEMBER BOTTLE STORE</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>167902</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Zambia</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Lusaka</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Makeni Villa Plot Bp184-005, Los Angels Road Park</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://bottleshopzm.com</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>300587</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>posbottleshop@gmail.com</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>320190007770</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-bottleshop-zambia/</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bottleshopzm</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bottleshopzm/</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>Suwilanji Kasanda</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>Director &amp; Partner</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/suwilanji-kasanda-4615bb31/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>BERKEMBER BOTTLE STORE</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>167902</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Zambia</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Lusaka</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Makeni Villa Plot Bp184-005, Los Angels Road Park</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://bottleshopzm.com</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>300587</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>posbottleshop@gmail.com</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>320190007770</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-bottleshop-zambia/</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bottleshopzm</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bottleshopzm/</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>Claudette Muloongo</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>Retail Manager</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/claudette-muloongo-4a9ba4151/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>DIAL A DOP LIMITED</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>167898</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Zambia</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Lusaka</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Chachacha Road Town Impala House</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dialadop.net, https://www.popsdialadop.co.za</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2104109</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>popslounge1@gmail.com</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>120170006550</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dialadopbluebottleliquors/</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCjJs-HiSKbnbjAzQf-TSxJQ</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Marlin Moodaley</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>DIAL A DOP LIMITED</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>167898</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Zambia</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Lusaka</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Chachacha Road Town Impala House</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dialadop.net, https://www.popsdialadop.co.za</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2104109</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>popslounge1@gmail.com</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>120170006550</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dialadopbluebottleliquors/</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCjJs-HiSKbnbjAzQf-TSxJQ</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Privilage Mashie</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>Distribution Manager</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
